--- a/public/static/公海客户导入模板.xlsx
+++ b/public/static/公海客户导入模板.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="27480" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="客户导入模板" sheetId="1" r:id="rId1"/>
+    <sheet name="公海客户导入模板" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -34,6 +34,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>客户编码</t>
     </r>
     <r>
@@ -49,6 +56,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>客户名称</t>
     </r>
     <r>
@@ -97,6 +111,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>电话</t>
     </r>
     <r>
@@ -112,6 +133,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>手机</t>
     </r>
     <r>
@@ -1418,24 +1446,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="13.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="12.1111111111111" customWidth="1"/>
-    <col min="8" max="8" width="10.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="7.88888888888889" customWidth="1"/>
+    <col min="2" max="2" width="18.225" customWidth="1"/>
+    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.225" customWidth="1"/>
+    <col min="6" max="6" width="13.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="12.1083333333333" customWidth="1"/>
+    <col min="8" max="8" width="10.225" customWidth="1"/>
+    <col min="9" max="9" width="7.89166666666667" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="8.22222222222222" customWidth="1"/>
-    <col min="12" max="12" width="10.1111111111111" customWidth="1"/>
+    <col min="11" max="11" width="8.225" customWidth="1"/>
+    <col min="12" max="12" width="10.1083333333333" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="16.7777777777778" customWidth="1"/>
+    <col min="14" max="14" width="16.775" customWidth="1"/>
     <col min="15" max="21" width="14.6666666666667" customWidth="1"/>
-    <col min="22" max="22" width="19.4444444444444" customWidth="1"/>
+    <col min="22" max="22" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:22">
@@ -1588,9 +1616,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="94.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="94.8916666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
